--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_6.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02252586343827574</v>
+        <v>0.01699001615672262</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008424069880698449</v>
+        <v>0.008419790512046258</v>
       </c>
       <c r="C2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>26847610</v>
+        <v>4268858</v>
       </c>
       <c r="L2" t="n">
-        <v>14913995</v>
+        <v>2205100</v>
       </c>
       <c r="M2" t="n">
-        <v>3643966</v>
+        <v>492154</v>
       </c>
       <c r="N2" t="n">
-        <v>187198</v>
+        <v>17979</v>
       </c>
       <c r="O2" t="n">
-        <v>2199092</v>
+        <v>295295</v>
       </c>
       <c r="P2" t="n">
-        <v>891292</v>
+        <v>121293</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999892115592957</v>
+        <v>0.9999911785125732</v>
       </c>
       <c r="R2" t="n">
-        <v>0.872797429561615</v>
+        <v>0.8249702453613281</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7501001954078674</v>
+        <v>0.6661277413368225</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6809710264205933</v>
+        <v>0.5828335881233215</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3677565157413483</v>
+        <v>0.1507192701101303</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7385218143463135</v>
+        <v>0.6419121623039246</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8136933445930481</v>
+        <v>0.7536067366600037</v>
       </c>
       <c r="X2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29140882</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17992178</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4814446</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>355185</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2757566</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080499</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564012289047241</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113964438438416</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578895330429077</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661842405796051</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019240140914917</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314445853233337</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005583088472464017</v>
+        <v>0.004093595341291732</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002018402068565029</v>
+        <v>0.002017893641709253</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>26847610</v>
+        <v>4268858</v>
       </c>
       <c r="E3" t="n">
-        <v>3470882</v>
+        <v>756271</v>
       </c>
       <c r="F3" t="n">
-        <v>92748</v>
+        <v>17518</v>
       </c>
       <c r="G3" t="n">
-        <v>14911</v>
+        <v>1805</v>
       </c>
       <c r="H3" t="n">
-        <v>5236</v>
+        <v>1079</v>
       </c>
       <c r="I3" t="n">
-        <v>324</v>
+        <v>46</v>
       </c>
       <c r="J3" t="n">
-        <v>60576303</v>
+        <v>10069564</v>
       </c>
       <c r="K3" t="n">
-        <v>64410668</v>
+        <v>10464718</v>
       </c>
       <c r="L3" t="n">
-        <v>74013615</v>
+        <v>12015564</v>
       </c>
       <c r="M3" t="n">
-        <v>91432206</v>
+        <v>15127847</v>
       </c>
       <c r="N3" t="n">
-        <v>97896291</v>
+        <v>16225187</v>
       </c>
       <c r="O3" t="n">
-        <v>94917699</v>
+        <v>15741276</v>
       </c>
       <c r="P3" t="n">
-        <v>97390857</v>
+        <v>16182903</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8822242617607117</v>
+        <v>0.8460589051246643</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7542640566825867</v>
+        <v>0.6691834330558777</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6488742232322693</v>
+        <v>0.5258668065071106</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3485476970672607</v>
+        <v>0.2008737027645111</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7189161777496338</v>
+        <v>0.5790154933929443</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7681770324707031</v>
+        <v>0.6270316243171692</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29140882</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1197602</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51676</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>41119</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60576714</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66995046</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77233139</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92341853</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>98036644</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95396441</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97515405</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575821757316589</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099408984184265</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572993874549866</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613260507583618</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014897346496582</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312487244606018</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05737529979919608</v>
+        <v>0.04569985360283699</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03188605624102609</v>
+        <v>0.03187338455984583</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3693026</v>
+        <v>853519</v>
       </c>
       <c r="E4" t="n">
-        <v>14913995</v>
+        <v>2205100</v>
       </c>
       <c r="F4" t="n">
-        <v>1019140</v>
+        <v>201830</v>
       </c>
       <c r="G4" t="n">
-        <v>48934</v>
+        <v>13001</v>
       </c>
       <c r="H4" t="n">
-        <v>89025</v>
+        <v>19769</v>
       </c>
       <c r="I4" t="n">
-        <v>8766</v>
+        <v>1987</v>
       </c>
       <c r="J4" t="n">
-        <v>411</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>3912803</v>
+        <v>905702</v>
       </c>
       <c r="L4" t="n">
-        <v>4968676</v>
+        <v>1105226</v>
       </c>
       <c r="M4" t="n">
-        <v>1707166</v>
+        <v>352262</v>
       </c>
       <c r="N4" t="n">
-        <v>321829</v>
+        <v>101309</v>
       </c>
       <c r="O4" t="n">
-        <v>778602</v>
+        <v>164729</v>
       </c>
       <c r="P4" t="n">
-        <v>204074</v>
+        <v>39657</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999945759773254</v>
+        <v>0.9999955892562866</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8774855136871338</v>
+        <v>0.8353815674781799</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7521763443946838</v>
+        <v>0.6676520705223083</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6645353436470032</v>
+        <v>0.5528866648674011</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3578945398330688</v>
+        <v>0.1722192615270615</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7285871505737305</v>
+        <v>0.6088437438011169</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7902804017066956</v>
+        <v>0.6845170259475708</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1240358</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17992178</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>499863</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33214</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6888</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1328425</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1749152</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>797519</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>181476</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299860</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79526</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569913744926453</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106681346893311</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575943112373352</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615840792655945</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017068147659302</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313466548919678</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>145311</v>
+        <v>35872</v>
       </c>
       <c r="E5" t="n">
-        <v>1276120</v>
+        <v>292419</v>
       </c>
       <c r="F5" t="n">
-        <v>3643966</v>
+        <v>492154</v>
       </c>
       <c r="G5" t="n">
-        <v>120532</v>
+        <v>33666</v>
       </c>
       <c r="H5" t="n">
-        <v>393978</v>
+        <v>73578</v>
       </c>
       <c r="I5" t="n">
-        <v>35909</v>
+        <v>8198</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3584119</v>
+        <v>776722</v>
       </c>
       <c r="L5" t="n">
-        <v>4858914</v>
+        <v>1090110</v>
       </c>
       <c r="M5" t="n">
-        <v>1971862</v>
+        <v>443737</v>
       </c>
       <c r="N5" t="n">
-        <v>349882</v>
+        <v>71525</v>
       </c>
       <c r="O5" t="n">
-        <v>859807</v>
+        <v>214700</v>
       </c>
       <c r="P5" t="n">
-        <v>268977</v>
+        <v>72147</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999958276748657</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.924085795879364</v>
+        <v>0.8975131511688232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9004853367805481</v>
+        <v>0.866268515586853</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9627459645271301</v>
+        <v>0.9515107870101929</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9931982159614563</v>
+        <v>0.9894716143608093</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9834094047546387</v>
+        <v>0.9768866300582886</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9952098727226257</v>
+        <v>0.9931893348693848</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48591</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>513866</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4814446</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59922</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175205</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1290847</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1780731</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>801382</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181895</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>301333</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79770</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734771251678467</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964256227016449</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838094711303711</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963204860687256</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122796058655</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983869791030884</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>69871</v>
+        <v>15021</v>
       </c>
       <c r="E6" t="n">
-        <v>95545</v>
+        <v>20926</v>
       </c>
       <c r="F6" t="n">
-        <v>116014</v>
+        <v>24346</v>
       </c>
       <c r="G6" t="n">
-        <v>187198</v>
+        <v>17979</v>
       </c>
       <c r="H6" t="n">
-        <v>61431</v>
+        <v>9993</v>
       </c>
       <c r="I6" t="n">
-        <v>6948</v>
+        <v>1223</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>39140</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32331</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65578</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>355185</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41960</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4412</v>
+        <v>1248</v>
       </c>
       <c r="E7" t="n">
-        <v>118132</v>
+        <v>33405</v>
       </c>
       <c r="F7" t="n">
-        <v>457126</v>
+        <v>102575</v>
       </c>
       <c r="G7" t="n">
-        <v>127917</v>
+        <v>49266</v>
       </c>
       <c r="H7" t="n">
-        <v>2199092</v>
+        <v>295295</v>
       </c>
       <c r="I7" t="n">
-        <v>152127</v>
+        <v>28203</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4867</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178417</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45627</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2757566</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72254</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>7997</v>
+        <v>2205</v>
       </c>
       <c r="F8" t="n">
-        <v>22138</v>
+        <v>5993</v>
       </c>
       <c r="G8" t="n">
-        <v>9535</v>
+        <v>3571</v>
       </c>
       <c r="H8" t="n">
-        <v>228932</v>
+        <v>60310</v>
       </c>
       <c r="I8" t="n">
-        <v>891292</v>
+        <v>121293</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1985</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1594</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75537</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080499</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
